--- a/data/xlsx/bmet--hotel-housekeeping.xlsx
+++ b/data/xlsx/bmet--hotel-housekeeping.xlsx
@@ -646,7 +646,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -668,7 +670,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -690,7 +694,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -724,7 +730,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -750,7 +758,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>3</v>
       </c>
@@ -772,7 +782,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -794,7 +806,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -820,7 +834,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -842,7 +858,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -864,7 +882,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -886,7 +906,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -908,7 +930,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -930,7 +954,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -952,7 +978,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -974,7 +1002,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>7</v>
       </c>
@@ -1000,7 +1030,9 @@
       <c r="C31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>7</v>
       </c>
@@ -1026,7 +1058,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -1048,7 +1082,9 @@
       <c r="C33" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>3</v>
       </c>
@@ -1070,7 +1106,9 @@
       <c r="C34" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>3</v>
       </c>
@@ -1092,7 +1130,9 @@
       <c r="C35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
@@ -1114,7 +1154,9 @@
       <c r="C36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>4</v>
       </c>
@@ -1136,7 +1178,9 @@
       <c r="C37" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>7</v>
       </c>
@@ -1158,7 +1202,9 @@
       <c r="C38" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>4</v>
       </c>
@@ -1180,7 +1226,9 @@
       <c r="C39" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>4</v>
       </c>
@@ -1202,7 +1250,9 @@
       <c r="C40" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>4</v>
       </c>
@@ -1224,7 +1274,9 @@
       <c r="C41" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>3</v>
       </c>
@@ -1246,7 +1298,9 @@
       <c r="C42" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="9" t="n"/>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="9" t="n">
         <v>3</v>
       </c>
